--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-16).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-16).xlsx
@@ -935,13 +935,13 @@
     <t>214</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 3.931,37</t>
-  </si>
-  <si>
-    <t>43.8</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 3.922,20</t>
+  </si>
+  <si>
+    <t>43.7</t>
   </si>
   <si>
     <t>27.1</t>
@@ -953,13 +953,13 @@
     <t>18.7</t>
   </si>
   <si>
-    <t>7.3</t>
+    <t>7.4</t>
   </si>
   <si>
     <t>5.9</t>
   </si>
   <si>
-    <t>42.4%</t>
+    <t>42.6%</t>
   </si>
   <si>
     <t>18.6%</t>
@@ -7621,7 +7621,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7651,14 +7651,26 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
+      <c r="M42" s="5">
+        <v>3695.7600000000002</v>
+      </c>
+      <c r="N42" s="6">
+        <v>48</v>
+      </c>
       <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
+      <c r="P42" s="7">
+        <v>5.8992914893617021</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>15.579796969696968</v>
+      </c>
+      <c r="R42" s="8">
+        <v>3.1919181818181817</v>
+      </c>
       <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
+      <c r="T42" s="9">
+        <v>0.54545454545454541</v>
+      </c>
       <c r="U42" s="9"/>
       <c r="V42" s="9"/>
       <c r="W42" s="9"/>
@@ -24467,7 +24479,7 @@
         <v>19847</v>
       </c>
       <c r="B156" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -24497,30 +24509,18 @@
         <v>58</v>
       </c>
       <c r="L156" s="4"/>
-      <c r="M156" s="5">
-        <v>3356.1100000000001</v>
-      </c>
-      <c r="N156" s="6">
-        <v>31</v>
-      </c>
+      <c r="M156" s="5"/>
+      <c r="N156" s="6"/>
       <c r="O156" s="6">
         <v>25</v>
       </c>
-      <c r="P156" s="7">
-        <v>7.0511099999999995</v>
-      </c>
-      <c r="Q156" s="8">
-        <v>17.330667999999999</v>
-      </c>
-      <c r="R156" s="8">
-        <v>3.2799999999999998</v>
-      </c>
+      <c r="P156" s="7"/>
+      <c r="Q156" s="8"/>
+      <c r="R156" s="8"/>
       <c r="S156" s="8">
         <v>7</v>
       </c>
-      <c r="T156" s="9">
-        <v>0.40000000000000002</v>
-      </c>
+      <c r="T156" s="9"/>
       <c r="U156" s="9">
         <v>0.16</v>
       </c>
@@ -31948,7 +31948,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -31978,14 +31978,26 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
+      <c r="M207" s="5">
+        <v>1940.98</v>
+      </c>
+      <c r="N207" s="6">
+        <v>24</v>
+      </c>
       <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
+      <c r="P207" s="7">
+        <v>6.2715291666666664</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>23.101669999999999</v>
+      </c>
+      <c r="R207" s="8">
+        <v>9.57667</v>
+      </c>
       <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
+      <c r="T207" s="9">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="U207" s="9"/>
       <c r="V207" s="9"/>
       <c r="W207" s="9"/>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-16).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-16).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 3.922,20</t>
-  </si>
-  <si>
-    <t>43.7</t>
-  </si>
-  <si>
-    <t>27.1</t>
-  </si>
-  <si>
-    <t>4.86</t>
-  </si>
-  <si>
-    <t>18.7</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 3.911,46</t>
+  </si>
+  <si>
+    <t>43.6</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>4.90</t>
+  </si>
+  <si>
+    <t>18.8</t>
   </si>
   <si>
     <t>7.4</t>
   </si>
   <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>42.6%</t>
-  </si>
-  <si>
-    <t>18.6%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>42.3%</t>
+  </si>
+  <si>
+    <t>18.4%</t>
   </si>
   <si>
     <t>2.3%</t>
@@ -980,7 +980,7 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>7.0%</t>
+    <t>6.9%</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -989,34 +989,34 @@
     <t>3.6%</t>
   </si>
   <si>
-    <t>1095.0</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>110.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>240.0</t>
-  </si>
-  <si>
-    <t>71.0</t>
+    <t>1105.0</t>
+  </si>
+  <si>
+    <t>894.0</t>
+  </si>
+  <si>
+    <t>112.0</t>
+  </si>
+  <si>
+    <t>31.0</t>
+  </si>
+  <si>
+    <t>241.0</t>
+  </si>
+  <si>
+    <t>73.0</t>
   </si>
   <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>332.0</t>
+    <t>334.0</t>
   </si>
   <si>
     <t>129.0</t>
   </si>
   <si>
-    <t>171.0</t>
+    <t>174.0</t>
   </si>
   <si>
     <t>0.7%</t>
@@ -7657,7 +7657,9 @@
       <c r="N42" s="6">
         <v>48</v>
       </c>
-      <c r="O42" s="6"/>
+      <c r="O42" s="6">
+        <v>33</v>
+      </c>
       <c r="P42" s="7">
         <v>5.8992914893617021</v>
       </c>
@@ -7667,31 +7669,75 @@
       <c r="R42" s="8">
         <v>3.1919181818181817</v>
       </c>
-      <c r="S42" s="8"/>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
       <c r="T42" s="9">
         <v>0.54545454545454541</v>
       </c>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="U42" s="9">
+        <v>0</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -16481,7 +16527,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16511,35 +16557,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>3507.5100000000002</v>
+      </c>
+      <c r="N102" s="6">
+        <v>34</v>
+      </c>
+      <c r="O102" s="6">
+        <v>25</v>
+      </c>
+      <c r="P102" s="7">
+        <v>9.8181382352941178</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>29.978000000000002</v>
+      </c>
+      <c r="R102" s="8">
+        <v>15.820291304347824</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -17752,7 +17856,9 @@
       <c r="N111" s="6">
         <v>8</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>7</v>
+      </c>
       <c r="P111" s="7">
         <v>5.8270875000000002</v>
       </c>
@@ -17762,31 +17868,75 @@
       <c r="R111" s="8">
         <v>1.7642857142857142</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.7142857142857143</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -24479,7 +24629,7 @@
         <v>19847</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -24509,18 +24659,30 @@
         <v>58</v>
       </c>
       <c r="L156" s="4"/>
-      <c r="M156" s="5"/>
-      <c r="N156" s="6"/>
+      <c r="M156" s="5">
+        <v>3356.1100000000001</v>
+      </c>
+      <c r="N156" s="6">
+        <v>31</v>
+      </c>
       <c r="O156" s="6">
         <v>25</v>
       </c>
-      <c r="P156" s="7"/>
-      <c r="Q156" s="8"/>
-      <c r="R156" s="8"/>
+      <c r="P156" s="7">
+        <v>7.0511099999999995</v>
+      </c>
+      <c r="Q156" s="8">
+        <v>17.330667999999999</v>
+      </c>
+      <c r="R156" s="8">
+        <v>3.2799999999999998</v>
+      </c>
       <c r="S156" s="8">
         <v>7</v>
       </c>
-      <c r="T156" s="9"/>
+      <c r="T156" s="9">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="U156" s="9">
         <v>0.16</v>
       </c>
@@ -30244,7 +30406,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30274,14 +30436,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>2936.8299999999999</v>
+      </c>
+      <c r="N195" s="6">
+        <v>37</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>3.9939805555555554</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>18.514814814814812</v>
+      </c>
+      <c r="R195" s="8">
+        <v>7.9153846153846157</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.18518518518518517</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
@@ -31984,7 +32158,9 @@
       <c r="N207" s="6">
         <v>24</v>
       </c>
-      <c r="O207" s="6"/>
+      <c r="O207" s="6">
+        <v>10</v>
+      </c>
       <c r="P207" s="7">
         <v>6.2715291666666664</v>
       </c>
@@ -31994,31 +32170,75 @@
       <c r="R207" s="8">
         <v>9.57667</v>
       </c>
-      <c r="S207" s="8"/>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
       <c r="T207" s="9">
         <v>0.40000000000000002</v>
       </c>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="U207" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-16).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-16).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 3.911,46</t>
-  </si>
-  <si>
-    <t>43.6</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>4.90</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 3.926,17</t>
+  </si>
+  <si>
+    <t>43.7</t>
+  </si>
+  <si>
+    <t>27.1</t>
+  </si>
+  <si>
+    <t>4.88</t>
   </si>
   <si>
     <t>18.8</t>
@@ -956,13 +956,13 @@
     <t>7.4</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>42.3%</t>
-  </si>
-  <si>
-    <t>18.4%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>41.6%</t>
+  </si>
+  <si>
+    <t>18.6%</t>
   </si>
   <si>
     <t>2.3%</t>
@@ -980,43 +980,43 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>6.9%</t>
+    <t>6.8%</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>1105.0</t>
-  </si>
-  <si>
-    <t>894.0</t>
-  </si>
-  <si>
-    <t>112.0</t>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>1144.0</t>
+  </si>
+  <si>
+    <t>928.0</t>
+  </si>
+  <si>
+    <t>114.0</t>
   </si>
   <si>
     <t>31.0</t>
   </si>
   <si>
-    <t>241.0</t>
-  </si>
-  <si>
-    <t>73.0</t>
+    <t>248.0</t>
+  </si>
+  <si>
+    <t>74.0</t>
   </si>
   <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>334.0</t>
-  </si>
-  <si>
-    <t>129.0</t>
-  </si>
-  <si>
-    <t>174.0</t>
+    <t>341.0</t>
+  </si>
+  <si>
+    <t>137.0</t>
+  </si>
+  <si>
+    <t>188.0</t>
   </si>
   <si>
     <t>0.7%</t>
@@ -3278,7 +3278,9 @@
       <c r="N13" s="6">
         <v>63</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>49</v>
+      </c>
       <c r="P13" s="7">
         <v>7.1706349206349209</v>
       </c>
@@ -3288,31 +3290,75 @@
       <c r="R13" s="8">
         <v>8.7152770833333335</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.22448979591836735</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.26530612244897961</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.061224489795918366</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.061224489795918366</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -10065,7 +10111,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10095,35 +10141,93 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="M58" s="5">
+        <v>4985.4899999999998</v>
+      </c>
+      <c r="N58" s="6">
+        <v>53</v>
+      </c>
+      <c r="O58" s="6">
+        <v>43</v>
+      </c>
+      <c r="P58" s="7">
+        <v>3.9731481481481485</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>19.236046511627908</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.9608534883720941</v>
+      </c>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
+      <c r="T58" s="9">
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="U58" s="9">
+        <v>0.13953488372093023</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.046511627906976744</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.046511627906976744</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.046511627906976744</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -12699,7 +12803,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12727,35 +12831,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>5558.9200000000001</v>
+      </c>
+      <c r="N76" s="6">
+        <v>61</v>
+      </c>
+      <c r="O76" s="6">
+        <v>25</v>
+      </c>
+      <c r="P76" s="7">
+        <v>3.4166672131147537</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>23.300668000000002</v>
+      </c>
+      <c r="R76" s="8">
+        <v>12.358695652173912</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.35999999999999999</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -28038,7 +28200,9 @@
       <c r="N179" s="6">
         <v>36</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>16</v>
+      </c>
       <c r="P179" s="7">
         <v>2.5540540540540539</v>
       </c>
@@ -28048,31 +28212,75 @@
       <c r="R179" s="8">
         <v>1.62395625</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.9375</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-16).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-16).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 3.926,17</t>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 3.929,29</t>
   </si>
   <si>
     <t>43.7</t>
@@ -950,16 +950,16 @@
     <t>4.88</t>
   </si>
   <si>
-    <t>18.8</t>
-  </si>
-  <si>
-    <t>7.4</t>
+    <t>18.9</t>
+  </si>
+  <si>
+    <t>7.5</t>
   </si>
   <si>
     <t>6.2</t>
   </si>
   <si>
-    <t>41.6%</t>
+    <t>41.7%</t>
   </si>
   <si>
     <t>18.6%</t>
@@ -4961,7 +4961,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4991,14 +4991,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>4476.5200000000004</v>
+      </c>
+      <c r="N24" s="6">
+        <v>50</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>4.831973469387755</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>25.160647222222224</v>
+      </c>
+      <c r="R24" s="8">
+        <v>13.464352777777778</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.1111111111111111</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -14776,7 +14788,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14804,14 +14816,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>3958.8099999999999</v>
+      </c>
+      <c r="N89" s="6">
+        <v>37</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>4.1708333333333334</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>22.87291875</v>
+      </c>
+      <c r="R89" s="8">
+        <v>9.3354187500000005</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.125</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
